--- a/modules.xlsx
+++ b/modules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Josh Murunga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C2861A5-CA0C-4550-8F48-CB07154B1F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762F2458-8DC5-4811-825E-77CFB1BA6F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7576F9BB-DBC4-4D03-8B1C-D88545B56239}"/>
   </bookViews>
@@ -1345,7 +1345,7 @@
         <v>90</v>
       </c>
       <c r="C44" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">

--- a/modules.xlsx
+++ b/modules.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Josh Murunga\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\josh\kenyaEMR-modules-updater\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762F2458-8DC5-4811-825E-77CFB1BA6F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BD5A41-01D6-49C3-B383-4D840EBA127D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7576F9BB-DBC4-4D03-8B1C-D88545B56239}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$32</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,71 +38,35 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="73">
   <si>
     <t>modules</t>
   </si>
   <si>
-    <t>addresshierarchy</t>
-  </si>
-  <si>
     <t>afyastat</t>
   </si>
   <si>
-    <t>appframework</t>
-  </si>
-  <si>
     <t>appointments</t>
   </si>
   <si>
-    <t>appui</t>
-  </si>
-  <si>
-    <t>attachments</t>
-  </si>
-  <si>
     <t>bedmanagement</t>
   </si>
   <si>
-    <t>calculation</t>
-  </si>
-  <si>
     <t>covid19</t>
   </si>
   <si>
     <t>crossborder2</t>
   </si>
   <si>
-    <t>dataexchange</t>
-  </si>
-  <si>
-    <t>emrapi</t>
-  </si>
-  <si>
     <t>event</t>
   </si>
   <si>
     <t>facilityreporting</t>
   </si>
   <si>
-    <t>fhir2</t>
-  </si>
-  <si>
-    <t>groovy</t>
-  </si>
-  <si>
     <t>hivtestingservices</t>
   </si>
   <si>
-    <t>htmlformentry</t>
-  </si>
-  <si>
-    <t>htmlwidgets</t>
-  </si>
-  <si>
-    <t>idgen</t>
-  </si>
-  <si>
     <t>initializer</t>
   </si>
   <si>
@@ -148,54 +112,15 @@
     <t>kenyaui</t>
   </si>
   <si>
-    <t>legacyui</t>
-  </si>
-  <si>
-    <t>metadatadeploy</t>
-  </si>
-  <si>
-    <t>metadatamapping</t>
-  </si>
-  <si>
-    <t>metadatasharing</t>
-  </si>
-  <si>
     <t>morgue</t>
   </si>
   <si>
-    <t>o3forms</t>
-  </si>
-  <si>
-    <t>openconceptlab</t>
-  </si>
-  <si>
     <t>orderexpansion</t>
   </si>
   <si>
-    <t>ordertemplates</t>
-  </si>
-  <si>
     <t>prep</t>
   </si>
   <si>
-    <t>queue</t>
-  </si>
-  <si>
-    <t>reporting</t>
-  </si>
-  <si>
-    <t>reportingcompatibility</t>
-  </si>
-  <si>
-    <t>reportingrest</t>
-  </si>
-  <si>
-    <t>serialization.xstream</t>
-  </si>
-  <si>
-    <t>spa</t>
-  </si>
-  <si>
     <t>spreadsheetimport</t>
   </si>
   <si>
@@ -205,12 +130,6 @@
     <t>teleconsultation</t>
   </si>
   <si>
-    <t>uicommons</t>
-  </si>
-  <si>
-    <t>uiframework</t>
-  </si>
-  <si>
     <t>vdot</t>
   </si>
   <si>
@@ -331,163 +250,10 @@
     <t>tag</t>
   </si>
   <si>
-    <t>2.18.0</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-addresshierarchy/archive/refs/tags/2.18.0.tar.gz</t>
-  </si>
-  <si>
-    <t>2.16.0</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-appframework/archive/refs/tags/2.16.0.tar.gz</t>
-  </si>
-  <si>
-    <t>1.13.0</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-appui/archive/refs/tags/1.13.0.tar.gz</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-attachments/archive/refs/tags/3.1.0.tar.gz</t>
-  </si>
-  <si>
-    <t>3.1.0</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-calculation/archive/refs/tags/1.2.1.tar.gz</t>
-  </si>
-  <si>
-    <t>1.2.1</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-dataexchange/archive/refs/tags/1.3.8.tar.gz</t>
-  </si>
-  <si>
-    <t>1.3.8</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-emrapi/archive/refs/tags/2.3.0.tar.gz</t>
-  </si>
-  <si>
-    <t>2.3.0</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-fhir2/archive/refs/tags/2.3.0.tar.gz</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-groovy/archive/refs/tags/2.3.1.tar.gz</t>
-  </si>
-  <si>
-    <t>2.3.1</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-htmlformentry/archive/refs/tags/5.3.0.tar.gz</t>
-  </si>
-  <si>
-    <t>5.3.0</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-htmlwidgets/archive/refs/tags/1.10.0.tar.gz</t>
-  </si>
-  <si>
-    <t>1.10.0</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-idgen/archive/refs/tags/4.10.0.tar.gz</t>
-  </si>
-  <si>
-    <t>4.10.0</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-legacyui/archive/refs/tags/1.15.0.tar.gz</t>
-  </si>
-  <si>
-    <t>1.15.0</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-metadatadeploy/archive/refs/tags/1.12.1.tar.gz</t>
-  </si>
-  <si>
-    <t>1.12.1</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-metadatamapping/archive/refs/tags/1.6.0.tar.gz</t>
-  </si>
-  <si>
-    <t>1.6.0</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-metadatasharing/archive/refs/tags/1.7.0.tar.gz</t>
-  </si>
-  <si>
-    <t>1.7.0</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-o3forms.git</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-openconceptlab/archive/refs/tags/2.2.0.tar.gz</t>
-  </si>
-  <si>
-    <t>2.2.0</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-ordertemplates/archive/refs/tags/v1.0.3.tar.gz</t>
-  </si>
-  <si>
-    <t>1.0.3</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-queue/archive/refs/tags/queue-2.6.0.tar.gz</t>
-  </si>
-  <si>
-    <t>2.6.0</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-reporting/archive/refs/tags/1.25.0.tar.gz</t>
-  </si>
-  <si>
-    <t>1.25.0</t>
-  </si>
-  <si>
     <t>https://github.com/palladiumkenya/openmrs-module-webservices.rest.git</t>
   </si>
   <si>
     <t>latest-web</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-reportingcompatibility/archive/refs/tags/2.0.9.tar.gz</t>
-  </si>
-  <si>
-    <t>2.0.9</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-reportingrest/archive/refs/tags/1.11.0.tar.gz</t>
-  </si>
-  <si>
-    <t>1.11.0</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-serialization.xstream/archive/refs/tags/0.2.15.tar.gz</t>
-  </si>
-  <si>
-    <t>0.2.15</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-spa.git</t>
-  </si>
-  <si>
-    <t>2.x</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-uicommons/archive/refs/tags/2.16.0.tar.gz</t>
-  </si>
-  <si>
-    <t>https://github.com/openmrs/openmrs-module-uiframework/archive/refs/tags/3.23.0.tar.gz</t>
-  </si>
-  <si>
-    <t>3.23.0</t>
   </si>
   <si>
     <t>https://github.com/makombe/openmrs-module-teleconsultation.git</t>
@@ -853,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}">
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
@@ -866,13 +632,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="D1" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -880,10 +646,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D2" t="s">
-        <v>97</v>
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -891,10 +657,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -902,10 +668,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" t="s">
-        <v>99</v>
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -913,10 +679,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -924,10 +690,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" t="s">
-        <v>101</v>
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -935,10 +701,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D7" t="s">
-        <v>104</v>
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -946,10 +712,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -957,10 +723,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D9" t="s">
-        <v>106</v>
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -968,10 +734,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -979,10 +745,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -990,10 +756,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D12" t="s">
-        <v>108</v>
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -1001,10 +767,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D13" t="s">
-        <v>110</v>
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -1012,10 +778,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -1023,10 +789,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -1034,546 +800,222 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D16" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+      <c r="C16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D17" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D19" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+      <c r="C19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D20" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D21" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="C25" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C26" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="C28" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="C29" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C30" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C33" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C34" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C35" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C36" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D37" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D38" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D39" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D40" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C41" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C42" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D43" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C44" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D45" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>45</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>46</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D47" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>47</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D48" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>48</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D49" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>49</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="D50" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>50</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D51" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>51</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C52" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>52</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C53" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>53</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C54" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>54</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C55" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>55</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D56" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>56</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D57" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>57</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C58" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>58</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C59" t="s">
-        <v>138</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D59" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}"/>
+  <autoFilter ref="A1:D32" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}"/>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{FB795B93-36B6-46BF-94E9-0038AB747753}"/>
-    <hyperlink ref="B5" r:id="rId2" xr:uid="{9B7024D0-965C-4E36-8BBD-D2B5693F8066}"/>
-    <hyperlink ref="B8" r:id="rId3" xr:uid="{7F49506F-F9DB-4218-A264-FD51A90A4108}"/>
-    <hyperlink ref="B10" r:id="rId4" xr:uid="{57F27C2F-EF1E-45D3-B84E-27C348EA6A19}"/>
-    <hyperlink ref="B11" r:id="rId5" xr:uid="{394E958F-8195-420D-9743-5785635638A1}"/>
-    <hyperlink ref="B14" r:id="rId6" xr:uid="{E82CC237-B326-4A72-8EE0-87587E9B3AE1}"/>
-    <hyperlink ref="B15" r:id="rId7" xr:uid="{01E3E2F4-7CAB-4169-96D6-AA9105700378}"/>
-    <hyperlink ref="B18" r:id="rId8" xr:uid="{FBE482EB-5021-4FB1-82FA-D062764CA1EB}"/>
-    <hyperlink ref="B22" r:id="rId9" xr:uid="{84CF3B0E-260C-4C31-86AA-03407F701080}"/>
-    <hyperlink ref="B23" r:id="rId10" xr:uid="{DBC906DF-0512-4F96-9980-1283786FC3BB}"/>
-    <hyperlink ref="B24" r:id="rId11" xr:uid="{30D882E1-E2EA-46AC-AADB-9448D1E01D5C}"/>
-    <hyperlink ref="B25" r:id="rId12" xr:uid="{6536EB8A-DA8E-4D0F-8593-FB4B5284D1A1}"/>
-    <hyperlink ref="B26" r:id="rId13" xr:uid="{6E470327-BDE8-411E-99F2-E8E5EC5BC4B5}"/>
-    <hyperlink ref="B27" r:id="rId14" xr:uid="{5CDDECC4-987C-4EF8-AAEE-D542DDB2E01A}"/>
-    <hyperlink ref="B28" r:id="rId15" xr:uid="{CB1A6B4D-F0B6-4F48-903E-DD67447B0D1E}"/>
-    <hyperlink ref="B29" r:id="rId16" xr:uid="{0A21E91B-C5AF-4E93-B298-37D3D20820BA}"/>
-    <hyperlink ref="B30" r:id="rId17" xr:uid="{82F1BD6D-109B-4F57-B429-F2C0A2DF5539}"/>
-    <hyperlink ref="B31" r:id="rId18" xr:uid="{CEFE724D-0289-4516-B679-5972075F9D45}"/>
-    <hyperlink ref="B32" r:id="rId19" xr:uid="{9E0376B5-01C2-4493-9DBE-E1898317C082}"/>
-    <hyperlink ref="B33" r:id="rId20" xr:uid="{5114C9EC-EEB3-4299-A9FD-2983F25CB21B}"/>
-    <hyperlink ref="B34" r:id="rId21" xr:uid="{8C48509F-21F4-4173-8B17-421ACD5D169D}"/>
-    <hyperlink ref="B35" r:id="rId22" xr:uid="{A430A9C6-FD58-4DE8-82B1-C2BDC43CD75D}"/>
-    <hyperlink ref="B36" r:id="rId23" xr:uid="{4BA87FC2-2482-47F3-AF0B-26573751D1D0}"/>
-    <hyperlink ref="B41" r:id="rId24" xr:uid="{CF736F36-5C13-46BF-8EFE-00A8F71CDBFA}"/>
-    <hyperlink ref="B44" r:id="rId25" xr:uid="{F3EE1F0F-3E4B-4FFA-A948-D718624032D3}"/>
-    <hyperlink ref="B46" r:id="rId26" xr:uid="{24CA94E5-1C41-4A90-8A88-F60639278F60}"/>
-    <hyperlink ref="B53" r:id="rId27" xr:uid="{4C1BA9E0-5C24-482B-895A-93E4FF6D7F94}"/>
-    <hyperlink ref="B54" r:id="rId28" xr:uid="{7F43F908-E262-4C52-A283-BC53176A8C46}"/>
-    <hyperlink ref="B58" r:id="rId29" xr:uid="{A55B142A-1F76-4FA4-8825-61B2F7CC0A1C}"/>
-    <hyperlink ref="B2" r:id="rId30" xr:uid="{06CE5437-216C-472A-9F84-AFE92FA55E98}"/>
-    <hyperlink ref="B4" r:id="rId31" xr:uid="{7DABD5EB-78CC-42F3-B658-A8579CF38AA8}"/>
-    <hyperlink ref="B6" r:id="rId32" xr:uid="{CA014124-F026-4F9D-AEDA-B7F311A41DF2}"/>
-    <hyperlink ref="B7" r:id="rId33" xr:uid="{D55EEDC7-5FB7-44E5-A4EE-FFC5776A0517}"/>
-    <hyperlink ref="B9" r:id="rId34" xr:uid="{BFDA1C5A-7691-4B0D-BFC1-DDE622723D35}"/>
-    <hyperlink ref="B12" r:id="rId35" xr:uid="{D687A617-B43F-4D21-B4CD-5A08A3257DAC}"/>
-    <hyperlink ref="B13" r:id="rId36" xr:uid="{558B6616-A538-43F1-990A-8D67DC1C556F}"/>
-    <hyperlink ref="B16" r:id="rId37" xr:uid="{9E03F2BB-309E-4388-91F5-8DE38CFF40DB}"/>
-    <hyperlink ref="B17" r:id="rId38" xr:uid="{69960FC0-A5A8-4F3C-8CF6-684AE359CCB3}"/>
-    <hyperlink ref="B19" r:id="rId39" xr:uid="{DF4DB416-910E-45EA-AB7B-0150431120CD}"/>
-    <hyperlink ref="B20" r:id="rId40" xr:uid="{5E9A3CD6-7D9F-4326-9DE3-DBD8CABB5C12}"/>
-    <hyperlink ref="B21" r:id="rId41" xr:uid="{A243A42C-3B2F-4A0D-AAC1-EEDFF718E594}"/>
-    <hyperlink ref="B37" r:id="rId42" xr:uid="{11048236-5DAD-4DD8-A31D-7F310536E6D8}"/>
-    <hyperlink ref="B38" r:id="rId43" xr:uid="{B92A338B-51D2-45CD-A3B9-6416070597FA}"/>
-    <hyperlink ref="B39" r:id="rId44" xr:uid="{5AF3CB4B-2794-49B3-ABF0-5D04E8DF09F3}"/>
-    <hyperlink ref="B40" r:id="rId45" xr:uid="{776D880C-F82D-4BC6-B16F-44A416D44D53}"/>
-    <hyperlink ref="B42" r:id="rId46" xr:uid="{A5EE8E0F-6D77-4586-A0DB-2E2D7D10BBB9}"/>
-    <hyperlink ref="B43" r:id="rId47" xr:uid="{AF0BFA86-490E-4676-97C5-E355BDC77E0A}"/>
-    <hyperlink ref="B45" r:id="rId48" xr:uid="{CDE3B66B-A3A6-4483-ADA2-7885D1081C4B}"/>
-    <hyperlink ref="B47" r:id="rId49" xr:uid="{8B615CC1-CE61-4D71-80BA-7A8AD88F5638}"/>
-    <hyperlink ref="B48" r:id="rId50" xr:uid="{A1A34841-DBFB-48BB-8DA8-397BC8A22E06}"/>
-    <hyperlink ref="B59" r:id="rId51" xr:uid="{C40CC3C2-AEB5-4CD8-88D8-C902A5085FAF}"/>
-    <hyperlink ref="B49" r:id="rId52" xr:uid="{BB5EF2D3-9062-48A2-8983-005F4CD60BD7}"/>
-    <hyperlink ref="B50" r:id="rId53" xr:uid="{DB0FB587-CF3C-421D-861A-651BC308D6F2}"/>
-    <hyperlink ref="B51" r:id="rId54" xr:uid="{BED3C8C5-69E2-4239-AD98-FAFB26DDEE24}"/>
-    <hyperlink ref="B52" r:id="rId55" xr:uid="{6224E60D-5660-421B-A878-7ADC099750CC}"/>
-    <hyperlink ref="B56" r:id="rId56" xr:uid="{22D71CFD-BE38-4667-8791-553740F1DF41}"/>
-    <hyperlink ref="B57" r:id="rId57" xr:uid="{289D2281-0A76-4B90-A51F-FAA77C22D4C9}"/>
-    <hyperlink ref="B55" r:id="rId58" xr:uid="{3B59B242-3FBC-42FA-A878-6E97732489BB}"/>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{FB795B93-36B6-46BF-94E9-0038AB747753}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{9B7024D0-965C-4E36-8BBD-D2B5693F8066}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{7F49506F-F9DB-4218-A264-FD51A90A4108}"/>
+    <hyperlink ref="B5" r:id="rId4" xr:uid="{57F27C2F-EF1E-45D3-B84E-27C348EA6A19}"/>
+    <hyperlink ref="B6" r:id="rId5" xr:uid="{394E958F-8195-420D-9743-5785635638A1}"/>
+    <hyperlink ref="B7" r:id="rId6" xr:uid="{E82CC237-B326-4A72-8EE0-87587E9B3AE1}"/>
+    <hyperlink ref="B8" r:id="rId7" xr:uid="{01E3E2F4-7CAB-4169-96D6-AA9105700378}"/>
+    <hyperlink ref="B9" r:id="rId8" xr:uid="{FBE482EB-5021-4FB1-82FA-D062764CA1EB}"/>
+    <hyperlink ref="B10" r:id="rId9" xr:uid="{84CF3B0E-260C-4C31-86AA-03407F701080}"/>
+    <hyperlink ref="B11" r:id="rId10" xr:uid="{DBC906DF-0512-4F96-9980-1283786FC3BB}"/>
+    <hyperlink ref="B12" r:id="rId11" xr:uid="{30D882E1-E2EA-46AC-AADB-9448D1E01D5C}"/>
+    <hyperlink ref="B13" r:id="rId12" xr:uid="{6536EB8A-DA8E-4D0F-8593-FB4B5284D1A1}"/>
+    <hyperlink ref="B14" r:id="rId13" xr:uid="{6E470327-BDE8-411E-99F2-E8E5EC5BC4B5}"/>
+    <hyperlink ref="B15" r:id="rId14" xr:uid="{5CDDECC4-987C-4EF8-AAEE-D542DDB2E01A}"/>
+    <hyperlink ref="B16" r:id="rId15" xr:uid="{CB1A6B4D-F0B6-4F48-903E-DD67447B0D1E}"/>
+    <hyperlink ref="B17" r:id="rId16" xr:uid="{0A21E91B-C5AF-4E93-B298-37D3D20820BA}"/>
+    <hyperlink ref="B18" r:id="rId17" xr:uid="{82F1BD6D-109B-4F57-B429-F2C0A2DF5539}"/>
+    <hyperlink ref="B19" r:id="rId18" xr:uid="{CEFE724D-0289-4516-B679-5972075F9D45}"/>
+    <hyperlink ref="B20" r:id="rId19" xr:uid="{9E0376B5-01C2-4493-9DBE-E1898317C082}"/>
+    <hyperlink ref="B21" r:id="rId20" xr:uid="{5114C9EC-EEB3-4299-A9FD-2983F25CB21B}"/>
+    <hyperlink ref="B22" r:id="rId21" xr:uid="{8C48509F-21F4-4173-8B17-421ACD5D169D}"/>
+    <hyperlink ref="B23" r:id="rId22" xr:uid="{A430A9C6-FD58-4DE8-82B1-C2BDC43CD75D}"/>
+    <hyperlink ref="B24" r:id="rId23" xr:uid="{4BA87FC2-2482-47F3-AF0B-26573751D1D0}"/>
+    <hyperlink ref="B25" r:id="rId24" xr:uid="{CF736F36-5C13-46BF-8EFE-00A8F71CDBFA}"/>
+    <hyperlink ref="B26" r:id="rId25" xr:uid="{F3EE1F0F-3E4B-4FFA-A948-D718624032D3}"/>
+    <hyperlink ref="B27" r:id="rId26" xr:uid="{24CA94E5-1C41-4A90-8A88-F60639278F60}"/>
+    <hyperlink ref="B28" r:id="rId27" xr:uid="{4C1BA9E0-5C24-482B-895A-93E4FF6D7F94}"/>
+    <hyperlink ref="B29" r:id="rId28" xr:uid="{7F43F908-E262-4C52-A283-BC53176A8C46}"/>
+    <hyperlink ref="B31" r:id="rId29" xr:uid="{A55B142A-1F76-4FA4-8825-61B2F7CC0A1C}"/>
+    <hyperlink ref="B32" r:id="rId30" xr:uid="{C40CC3C2-AEB5-4CD8-88D8-C902A5085FAF}"/>
+    <hyperlink ref="B30" r:id="rId31" xr:uid="{3B59B242-3FBC-42FA-A878-6E97732489BB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/modules.xlsx
+++ b/modules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\josh\kenyaEMR-modules-updater\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BD5A41-01D6-49C3-B383-4D840EBA127D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434E4C1F-63B6-4BC4-AB7D-22751BB99743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7576F9BB-DBC4-4D03-8B1C-D88545B56239}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="71">
   <si>
     <t>modules</t>
   </si>
@@ -103,9 +103,6 @@
     <t>kenyaemrorderentry</t>
   </si>
   <si>
-    <t>kenyaemrpsmart</t>
-  </si>
-  <si>
     <t>kenyakeypop</t>
   </si>
   <si>
@@ -215,9 +212,6 @@
   </si>
   <si>
     <t>https://github.com/palladiumkenya/openmrs-module-kenyaemrorderentry.git</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-kenyaemrpsmart.git</t>
   </si>
   <si>
     <t>https://github.com/palladiumkenya/openmrs-module-kenyakeypop.git</t>
@@ -619,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
@@ -632,13 +626,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s">
         <v>32</v>
       </c>
-      <c r="C1" t="s">
-        <v>33</v>
-      </c>
       <c r="D1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -646,10 +640,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -657,10 +651,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
         <v>36</v>
-      </c>
-      <c r="C3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -668,10 +662,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -679,10 +673,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -690,10 +684,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
         <v>40</v>
-      </c>
-      <c r="C6" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -701,10 +695,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -712,10 +706,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -723,10 +717,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -734,10 +728,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
         <v>45</v>
-      </c>
-      <c r="C10" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -745,10 +739,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -756,10 +750,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s">
         <v>48</v>
-      </c>
-      <c r="C12" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -767,10 +761,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -778,10 +772,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -789,10 +783,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -800,10 +794,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -811,10 +805,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -822,10 +816,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -833,10 +827,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -844,10 +838,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -855,10 +849,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -866,10 +860,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -877,10 +871,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -888,10 +882,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -899,10 +893,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -910,10 +904,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -921,10 +915,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -932,10 +926,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" t="s">
         <v>65</v>
-      </c>
-      <c r="C28" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -943,10 +937,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -954,10 +948,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C30" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -968,22 +962,11 @@
         <v>68</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C32" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D32" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}"/>
+  <autoFilter ref="A1:D31" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{FB795B93-36B6-46BF-94E9-0038AB747753}"/>
     <hyperlink ref="B3" r:id="rId2" xr:uid="{9B7024D0-965C-4E36-8BBD-D2B5693F8066}"/>
@@ -1005,17 +988,16 @@
     <hyperlink ref="B19" r:id="rId18" xr:uid="{CEFE724D-0289-4516-B679-5972075F9D45}"/>
     <hyperlink ref="B20" r:id="rId19" xr:uid="{9E0376B5-01C2-4493-9DBE-E1898317C082}"/>
     <hyperlink ref="B21" r:id="rId20" xr:uid="{5114C9EC-EEB3-4299-A9FD-2983F25CB21B}"/>
-    <hyperlink ref="B22" r:id="rId21" xr:uid="{8C48509F-21F4-4173-8B17-421ACD5D169D}"/>
-    <hyperlink ref="B23" r:id="rId22" xr:uid="{A430A9C6-FD58-4DE8-82B1-C2BDC43CD75D}"/>
-    <hyperlink ref="B24" r:id="rId23" xr:uid="{4BA87FC2-2482-47F3-AF0B-26573751D1D0}"/>
-    <hyperlink ref="B25" r:id="rId24" xr:uid="{CF736F36-5C13-46BF-8EFE-00A8F71CDBFA}"/>
-    <hyperlink ref="B26" r:id="rId25" xr:uid="{F3EE1F0F-3E4B-4FFA-A948-D718624032D3}"/>
-    <hyperlink ref="B27" r:id="rId26" xr:uid="{24CA94E5-1C41-4A90-8A88-F60639278F60}"/>
-    <hyperlink ref="B28" r:id="rId27" xr:uid="{4C1BA9E0-5C24-482B-895A-93E4FF6D7F94}"/>
-    <hyperlink ref="B29" r:id="rId28" xr:uid="{7F43F908-E262-4C52-A283-BC53176A8C46}"/>
-    <hyperlink ref="B31" r:id="rId29" xr:uid="{A55B142A-1F76-4FA4-8825-61B2F7CC0A1C}"/>
-    <hyperlink ref="B32" r:id="rId30" xr:uid="{C40CC3C2-AEB5-4CD8-88D8-C902A5085FAF}"/>
-    <hyperlink ref="B30" r:id="rId31" xr:uid="{3B59B242-3FBC-42FA-A878-6E97732489BB}"/>
+    <hyperlink ref="B22" r:id="rId21" xr:uid="{A430A9C6-FD58-4DE8-82B1-C2BDC43CD75D}"/>
+    <hyperlink ref="B23" r:id="rId22" xr:uid="{4BA87FC2-2482-47F3-AF0B-26573751D1D0}"/>
+    <hyperlink ref="B24" r:id="rId23" xr:uid="{CF736F36-5C13-46BF-8EFE-00A8F71CDBFA}"/>
+    <hyperlink ref="B25" r:id="rId24" xr:uid="{F3EE1F0F-3E4B-4FFA-A948-D718624032D3}"/>
+    <hyperlink ref="B26" r:id="rId25" xr:uid="{24CA94E5-1C41-4A90-8A88-F60639278F60}"/>
+    <hyperlink ref="B27" r:id="rId26" xr:uid="{4C1BA9E0-5C24-482B-895A-93E4FF6D7F94}"/>
+    <hyperlink ref="B28" r:id="rId27" xr:uid="{7F43F908-E262-4C52-A283-BC53176A8C46}"/>
+    <hyperlink ref="B30" r:id="rId28" xr:uid="{A55B142A-1F76-4FA4-8825-61B2F7CC0A1C}"/>
+    <hyperlink ref="B31" r:id="rId29" xr:uid="{C40CC3C2-AEB5-4CD8-88D8-C902A5085FAF}"/>
+    <hyperlink ref="B29" r:id="rId30" xr:uid="{3B59B242-3FBC-42FA-A878-6E97732489BB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/modules.xlsx
+++ b/modules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\josh\kenyaEMR-modules-updater\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434E4C1F-63B6-4BC4-AB7D-22751BB99743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C2585C-D17B-4E57-B6A7-E8ED4D00B16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7576F9BB-DBC4-4D03-8B1C-D88545B56239}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="69">
   <si>
     <t>modules</t>
   </si>
@@ -118,9 +118,6 @@
     <t>prep</t>
   </si>
   <si>
-    <t>spreadsheetimport</t>
-  </si>
-  <si>
     <t>stockmanagement</t>
   </si>
   <si>
@@ -227,9 +224,6 @@
   </si>
   <si>
     <t>https://github.com/palladiumkenya/openmrs-module-prep.git</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-spreadsheetimport.git</t>
   </si>
   <si>
     <t>https://github.com/palladiumkenya/openmrs-module-commodity.git</t>
@@ -613,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
@@ -626,13 +620,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" t="s">
         <v>31</v>
       </c>
-      <c r="C1" t="s">
-        <v>32</v>
-      </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -640,10 +634,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -651,10 +645,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
         <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -662,10 +656,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -673,10 +667,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -684,10 +678,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
         <v>39</v>
-      </c>
-      <c r="C6" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -695,10 +689,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -706,10 +700,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -717,10 +711,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -728,10 +722,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
         <v>44</v>
-      </c>
-      <c r="C10" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -739,10 +733,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -750,10 +744,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" t="s">
         <v>47</v>
-      </c>
-      <c r="C12" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -761,10 +755,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -772,10 +766,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -783,10 +777,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -794,10 +788,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -805,10 +799,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -816,10 +810,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -827,10 +821,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -838,10 +832,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -849,10 +843,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -860,10 +854,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -871,10 +865,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -882,10 +876,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -893,10 +887,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -904,10 +898,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -915,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" t="s">
         <v>63</v>
-      </c>
-      <c r="C27" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -926,10 +920,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -937,10 +931,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C29" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -951,22 +945,11 @@
         <v>66</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C31" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D31" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}"/>
+  <autoFilter ref="A1:D30" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{FB795B93-36B6-46BF-94E9-0038AB747753}"/>
     <hyperlink ref="B3" r:id="rId2" xr:uid="{9B7024D0-965C-4E36-8BBD-D2B5693F8066}"/>
@@ -993,11 +976,10 @@
     <hyperlink ref="B24" r:id="rId23" xr:uid="{CF736F36-5C13-46BF-8EFE-00A8F71CDBFA}"/>
     <hyperlink ref="B25" r:id="rId24" xr:uid="{F3EE1F0F-3E4B-4FFA-A948-D718624032D3}"/>
     <hyperlink ref="B26" r:id="rId25" xr:uid="{24CA94E5-1C41-4A90-8A88-F60639278F60}"/>
-    <hyperlink ref="B27" r:id="rId26" xr:uid="{4C1BA9E0-5C24-482B-895A-93E4FF6D7F94}"/>
-    <hyperlink ref="B28" r:id="rId27" xr:uid="{7F43F908-E262-4C52-A283-BC53176A8C46}"/>
-    <hyperlink ref="B30" r:id="rId28" xr:uid="{A55B142A-1F76-4FA4-8825-61B2F7CC0A1C}"/>
-    <hyperlink ref="B31" r:id="rId29" xr:uid="{C40CC3C2-AEB5-4CD8-88D8-C902A5085FAF}"/>
-    <hyperlink ref="B29" r:id="rId30" xr:uid="{3B59B242-3FBC-42FA-A878-6E97732489BB}"/>
+    <hyperlink ref="B27" r:id="rId26" xr:uid="{7F43F908-E262-4C52-A283-BC53176A8C46}"/>
+    <hyperlink ref="B29" r:id="rId27" xr:uid="{A55B142A-1F76-4FA4-8825-61B2F7CC0A1C}"/>
+    <hyperlink ref="B30" r:id="rId28" xr:uid="{C40CC3C2-AEB5-4CD8-88D8-C902A5085FAF}"/>
+    <hyperlink ref="B28" r:id="rId29" xr:uid="{3B59B242-3FBC-42FA-A878-6E97732489BB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/modules.xlsx
+++ b/modules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\josh\kenyaEMR-modules-updater\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C2585C-D17B-4E57-B6A7-E8ED4D00B16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12AB14E5-F20B-4688-918D-0D882208940F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7576F9BB-DBC4-4D03-8B1C-D88545B56239}"/>
   </bookViews>
@@ -241,10 +241,10 @@
     <t>https://github.com/palladiumkenya/openmrs-module-webservices.rest.git</t>
   </si>
   <si>
-    <t>latest-web</t>
-  </si>
-  <si>
     <t>https://github.com/makombe/openmrs-module-teleconsultation.git</t>
+  </si>
+  <si>
+    <t>version-2.51.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -920,7 +920,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C28" t="s">
         <v>39</v>
@@ -945,7 +945,7 @@
         <v>66</v>
       </c>
       <c r="C30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/modules.xlsx
+++ b/modules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\josh\kenyaEMR-modules-updater\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12AB14E5-F20B-4688-918D-0D882208940F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4474EEB0-4E9C-4462-830B-533E6E3A8102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7576F9BB-DBC4-4D03-8B1C-D88545B56239}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="72">
   <si>
     <t>modules</t>
   </si>
@@ -245,6 +245,15 @@
   </si>
   <si>
     <t>version-2.51.0-SNAPSHOT</t>
+  </si>
+  <si>
+    <t>https://github.com/palladiumkenya/openmrs-module-queue.git</t>
+  </si>
+  <si>
+    <t>queue</t>
+  </si>
+  <si>
+    <t>queues-v2</t>
   </si>
 </sst>
 </file>
@@ -607,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
@@ -946,6 +955,17 @@
       </c>
       <c r="C30" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -980,6 +1000,7 @@
     <hyperlink ref="B29" r:id="rId27" xr:uid="{A55B142A-1F76-4FA4-8825-61B2F7CC0A1C}"/>
     <hyperlink ref="B30" r:id="rId28" xr:uid="{C40CC3C2-AEB5-4CD8-88D8-C902A5085FAF}"/>
     <hyperlink ref="B28" r:id="rId29" xr:uid="{3B59B242-3FBC-42FA-A878-6E97732489BB}"/>
+    <hyperlink ref="B31" r:id="rId30" xr:uid="{9911E7B8-06C5-456A-9C67-209E377DE4D4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/modules.xlsx
+++ b/modules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\josh\kenyaEMR-modules-updater\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4474EEB0-4E9C-4462-830B-533E6E3A8102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E490BAB4-124D-4B95-ADE7-261E9123F9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7576F9BB-DBC4-4D03-8B1C-D88545B56239}"/>
   </bookViews>
@@ -244,9 +244,6 @@
     <t>https://github.com/makombe/openmrs-module-teleconsultation.git</t>
   </si>
   <si>
-    <t>version-2.51.0-SNAPSHOT</t>
-  </si>
-  <si>
     <t>https://github.com/palladiumkenya/openmrs-module-queue.git</t>
   </si>
   <si>
@@ -254,6 +251,9 @@
   </si>
   <si>
     <t>queues-v2</t>
+  </si>
+  <si>
+    <t>version-2.55.0-snapshot</t>
   </si>
 </sst>
 </file>
@@ -954,18 +954,18 @@
         <v>66</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C31" t="s">
         <v>70</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C31" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/modules.xlsx
+++ b/modules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\josh\kenyaEMR-modules-updater\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E490BAB4-124D-4B95-ADE7-261E9123F9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1418CF-F7A3-45B7-954F-750C2A41E676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7576F9BB-DBC4-4D03-8B1C-D88545B56239}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="76">
   <si>
     <t>modules</t>
   </si>
@@ -254,6 +254,18 @@
   </si>
   <si>
     <t>version-2.55.0-snapshot</t>
+  </si>
+  <si>
+    <t>serialization</t>
+  </si>
+  <si>
+    <t>https://github.com/palladiumkenya/openmrs-module-serialization.xstream.git</t>
+  </si>
+  <si>
+    <t>stocks</t>
+  </si>
+  <si>
+    <t>stock-2.8.1-platform</t>
   </si>
 </sst>
 </file>
@@ -616,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
@@ -966,6 +978,28 @@
       </c>
       <c r="C31" t="s">
         <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1001,6 +1035,8 @@
     <hyperlink ref="B30" r:id="rId28" xr:uid="{C40CC3C2-AEB5-4CD8-88D8-C902A5085FAF}"/>
     <hyperlink ref="B28" r:id="rId29" xr:uid="{3B59B242-3FBC-42FA-A878-6E97732489BB}"/>
     <hyperlink ref="B31" r:id="rId30" xr:uid="{9911E7B8-06C5-456A-9C67-209E377DE4D4}"/>
+    <hyperlink ref="B32" r:id="rId31" xr:uid="{8D06A38D-AAD3-41FE-BDFB-143E0E3CB246}"/>
+    <hyperlink ref="B33" r:id="rId32" xr:uid="{6A8AB9E9-C98F-411D-AEE3-133806E23CE8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/modules.xlsx
+++ b/modules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\josh\kenyaEMR-modules-updater\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C1418CF-F7A3-45B7-954F-750C2A41E676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D764FFF-16C5-4BF8-B750-5A4895EACD85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7576F9BB-DBC4-4D03-8B1C-D88545B56239}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="64">
   <si>
     <t>modules</t>
   </si>
@@ -49,27 +49,15 @@
     <t>appointments</t>
   </si>
   <si>
-    <t>bedmanagement</t>
-  </si>
-  <si>
     <t>covid19</t>
   </si>
   <si>
     <t>crossborder2</t>
   </si>
   <si>
-    <t>event</t>
-  </si>
-  <si>
-    <t>facilityreporting</t>
-  </si>
-  <si>
     <t>hivtestingservices</t>
   </si>
   <si>
-    <t>initializer</t>
-  </si>
-  <si>
     <t>insuranceclaims</t>
   </si>
   <si>
@@ -127,145 +115,121 @@
     <t>vdot</t>
   </si>
   <si>
-    <t>webservices.rest</t>
-  </si>
-  <si>
     <t>git_repo</t>
   </si>
   <si>
     <t>branch</t>
   </si>
   <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-afyastat.git</t>
-  </si>
-  <si>
     <t>master</t>
   </si>
   <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-appointments.git</t>
-  </si>
-  <si>
     <t>appointment-v2</t>
   </si>
   <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-bedmanagement.git</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-covid19.git</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-crossborder2.git</t>
-  </si>
-  <si>
     <t>main</t>
   </si>
   <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-event.git</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-facilityreporting.git</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-kenyaemrhivtesting.git</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-initializer.git</t>
-  </si>
-  <si>
-    <t>v2.9.0</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-insuranceclaims.git</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-jasperreports.git</t>
-  </si>
-  <si>
     <t>develop</t>
   </si>
   <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-kenyacore.git</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-kenyadq.git</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-kenyaemr.git</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-kenyaEMRCashier.git</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-kenyaEMRChart.git</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-kenyaemrIL.git</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-kenyaemrextras.git</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-kenyaemr-machine-learning.git</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-kenyaemrorderentry.git</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-kenyakeypop.git</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-kenyaui.git</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-morgue.git</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-orderexpansion.git</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-prep.git</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-commodity.git</t>
-  </si>
-  <si>
-    <t>stock-v2</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-vdot.git</t>
-  </si>
-  <si>
     <t>tag</t>
   </si>
   <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-webservices.rest.git</t>
-  </si>
-  <si>
     <t>https://github.com/makombe/openmrs-module-teleconsultation.git</t>
   </si>
   <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-queue.git</t>
-  </si>
-  <si>
     <t>queue</t>
   </si>
   <si>
     <t>queues-v2</t>
   </si>
   <si>
-    <t>version-2.55.0-snapshot</t>
-  </si>
-  <si>
-    <t>serialization</t>
-  </si>
-  <si>
-    <t>https://github.com/palladiumkenya/openmrs-module-serialization.xstream.git</t>
-  </si>
-  <si>
-    <t>stocks</t>
-  </si>
-  <si>
-    <t>stock-2.8.1-platform</t>
+    <t>stock-2.8.4-platform</t>
+  </si>
+  <si>
+    <t>kenyaemrpsmart</t>
+  </si>
+  <si>
+    <t>spreadsheetimport</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-kenyaemrpsmart.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-spreadsheetimport.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-afyastat.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-appointments.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-covid19.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-crossborder2.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-kenyaemrhivtesting.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-insuranceclaims.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-jasperreports.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-kenyacore.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-kenyadq.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-kenyaemr.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-kenyaEMRCashier.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-kenyaEMRChart.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-kenyaemrIL.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-kenyaemrextras.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-kenyaemr-machine-learning.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-kenyaemrorderentry.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-kenyakeypop.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-kenyaui.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-morgue.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-orderexpansion.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-prep.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-queue.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-commodity.git</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-vdot.git</t>
   </si>
 </sst>
 </file>
@@ -628,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}">
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
@@ -641,13 +605,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s">
         <v>31</v>
-      </c>
-      <c r="D1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -655,10 +619,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -666,10 +630,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -677,10 +641,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -688,10 +652,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -699,10 +663,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -710,10 +674,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -721,10 +685,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -732,10 +696,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -743,10 +707,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -754,10 +718,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -765,10 +729,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -776,10 +740,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -787,10 +751,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -798,10 +762,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -809,10 +773,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -820,223 +784,163 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C30" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>69</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C31" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>72</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>74</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C33" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D30" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}"/>
+  <autoFilter ref="A1:D28" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{FB795B93-36B6-46BF-94E9-0038AB747753}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{9B7024D0-965C-4E36-8BBD-D2B5693F8066}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{7F49506F-F9DB-4218-A264-FD51A90A4108}"/>
-    <hyperlink ref="B5" r:id="rId4" xr:uid="{57F27C2F-EF1E-45D3-B84E-27C348EA6A19}"/>
-    <hyperlink ref="B6" r:id="rId5" xr:uid="{394E958F-8195-420D-9743-5785635638A1}"/>
-    <hyperlink ref="B7" r:id="rId6" xr:uid="{E82CC237-B326-4A72-8EE0-87587E9B3AE1}"/>
-    <hyperlink ref="B8" r:id="rId7" xr:uid="{01E3E2F4-7CAB-4169-96D6-AA9105700378}"/>
-    <hyperlink ref="B9" r:id="rId8" xr:uid="{FBE482EB-5021-4FB1-82FA-D062764CA1EB}"/>
-    <hyperlink ref="B10" r:id="rId9" xr:uid="{84CF3B0E-260C-4C31-86AA-03407F701080}"/>
-    <hyperlink ref="B11" r:id="rId10" xr:uid="{DBC906DF-0512-4F96-9980-1283786FC3BB}"/>
-    <hyperlink ref="B12" r:id="rId11" xr:uid="{30D882E1-E2EA-46AC-AADB-9448D1E01D5C}"/>
-    <hyperlink ref="B13" r:id="rId12" xr:uid="{6536EB8A-DA8E-4D0F-8593-FB4B5284D1A1}"/>
-    <hyperlink ref="B14" r:id="rId13" xr:uid="{6E470327-BDE8-411E-99F2-E8E5EC5BC4B5}"/>
-    <hyperlink ref="B15" r:id="rId14" xr:uid="{5CDDECC4-987C-4EF8-AAEE-D542DDB2E01A}"/>
-    <hyperlink ref="B16" r:id="rId15" xr:uid="{CB1A6B4D-F0B6-4F48-903E-DD67447B0D1E}"/>
-    <hyperlink ref="B17" r:id="rId16" xr:uid="{0A21E91B-C5AF-4E93-B298-37D3D20820BA}"/>
-    <hyperlink ref="B18" r:id="rId17" xr:uid="{82F1BD6D-109B-4F57-B429-F2C0A2DF5539}"/>
-    <hyperlink ref="B19" r:id="rId18" xr:uid="{CEFE724D-0289-4516-B679-5972075F9D45}"/>
-    <hyperlink ref="B20" r:id="rId19" xr:uid="{9E0376B5-01C2-4493-9DBE-E1898317C082}"/>
-    <hyperlink ref="B21" r:id="rId20" xr:uid="{5114C9EC-EEB3-4299-A9FD-2983F25CB21B}"/>
-    <hyperlink ref="B22" r:id="rId21" xr:uid="{A430A9C6-FD58-4DE8-82B1-C2BDC43CD75D}"/>
-    <hyperlink ref="B23" r:id="rId22" xr:uid="{4BA87FC2-2482-47F3-AF0B-26573751D1D0}"/>
-    <hyperlink ref="B24" r:id="rId23" xr:uid="{CF736F36-5C13-46BF-8EFE-00A8F71CDBFA}"/>
-    <hyperlink ref="B25" r:id="rId24" xr:uid="{F3EE1F0F-3E4B-4FFA-A948-D718624032D3}"/>
-    <hyperlink ref="B26" r:id="rId25" xr:uid="{24CA94E5-1C41-4A90-8A88-F60639278F60}"/>
-    <hyperlink ref="B27" r:id="rId26" xr:uid="{7F43F908-E262-4C52-A283-BC53176A8C46}"/>
-    <hyperlink ref="B29" r:id="rId27" xr:uid="{A55B142A-1F76-4FA4-8825-61B2F7CC0A1C}"/>
-    <hyperlink ref="B30" r:id="rId28" xr:uid="{C40CC3C2-AEB5-4CD8-88D8-C902A5085FAF}"/>
-    <hyperlink ref="B28" r:id="rId29" xr:uid="{3B59B242-3FBC-42FA-A878-6E97732489BB}"/>
-    <hyperlink ref="B31" r:id="rId30" xr:uid="{9911E7B8-06C5-456A-9C67-209E377DE4D4}"/>
-    <hyperlink ref="B32" r:id="rId31" xr:uid="{8D06A38D-AAD3-41FE-BDFB-143E0E3CB246}"/>
-    <hyperlink ref="B33" r:id="rId32" xr:uid="{6A8AB9E9-C98F-411D-AEE3-133806E23CE8}"/>
+    <hyperlink ref="B4" r:id="rId2" xr:uid="{57F27C2F-EF1E-45D3-B84E-27C348EA6A19}"/>
+    <hyperlink ref="B5" r:id="rId3" xr:uid="{394E958F-8195-420D-9743-5785635638A1}"/>
+    <hyperlink ref="B6" r:id="rId4" xr:uid="{FBE482EB-5021-4FB1-82FA-D062764CA1EB}"/>
+    <hyperlink ref="B7" r:id="rId5" xr:uid="{DBC906DF-0512-4F96-9980-1283786FC3BB}"/>
+    <hyperlink ref="B8" r:id="rId6" xr:uid="{30D882E1-E2EA-46AC-AADB-9448D1E01D5C}"/>
+    <hyperlink ref="B9" r:id="rId7" xr:uid="{6536EB8A-DA8E-4D0F-8593-FB4B5284D1A1}"/>
+    <hyperlink ref="B10" r:id="rId8" xr:uid="{6E470327-BDE8-411E-99F2-E8E5EC5BC4B5}"/>
+    <hyperlink ref="B11" r:id="rId9" xr:uid="{5CDDECC4-987C-4EF8-AAEE-D542DDB2E01A}"/>
+    <hyperlink ref="B12" r:id="rId10" xr:uid="{CB1A6B4D-F0B6-4F48-903E-DD67447B0D1E}"/>
+    <hyperlink ref="B13" r:id="rId11" xr:uid="{0A21E91B-C5AF-4E93-B298-37D3D20820BA}"/>
+    <hyperlink ref="B14" r:id="rId12" xr:uid="{82F1BD6D-109B-4F57-B429-F2C0A2DF5539}"/>
+    <hyperlink ref="B15" r:id="rId13" xr:uid="{CEFE724D-0289-4516-B679-5972075F9D45}"/>
+    <hyperlink ref="B16" r:id="rId14" xr:uid="{9E0376B5-01C2-4493-9DBE-E1898317C082}"/>
+    <hyperlink ref="B17" r:id="rId15" xr:uid="{5114C9EC-EEB3-4299-A9FD-2983F25CB21B}"/>
+    <hyperlink ref="B19" r:id="rId16" xr:uid="{A430A9C6-FD58-4DE8-82B1-C2BDC43CD75D}"/>
+    <hyperlink ref="B20" r:id="rId17" xr:uid="{4BA87FC2-2482-47F3-AF0B-26573751D1D0}"/>
+    <hyperlink ref="B21" r:id="rId18" xr:uid="{CF736F36-5C13-46BF-8EFE-00A8F71CDBFA}"/>
+    <hyperlink ref="B22" r:id="rId19" xr:uid="{F3EE1F0F-3E4B-4FFA-A948-D718624032D3}"/>
+    <hyperlink ref="B23" r:id="rId20" xr:uid="{24CA94E5-1C41-4A90-8A88-F60639278F60}"/>
+    <hyperlink ref="B28" r:id="rId21" xr:uid="{A55B142A-1F76-4FA4-8825-61B2F7CC0A1C}"/>
+    <hyperlink ref="B27" r:id="rId22" xr:uid="{3B59B242-3FBC-42FA-A878-6E97732489BB}"/>
+    <hyperlink ref="B26" r:id="rId23" xr:uid="{7F43F908-E262-4C52-A283-BC53176A8C46}"/>
+    <hyperlink ref="B24" r:id="rId24" xr:uid="{9911E7B8-06C5-456A-9C67-209E377DE4D4}"/>
+    <hyperlink ref="B3" r:id="rId25" xr:uid="{9B7024D0-965C-4E36-8BBD-D2B5693F8066}"/>
+    <hyperlink ref="B18" r:id="rId26" xr:uid="{5790DF07-3821-4131-B34A-23B6360A489F}"/>
+    <hyperlink ref="B25" r:id="rId27" xr:uid="{4AEA6BB0-8BA5-4D64-85BA-BBC654A24D26}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/modules.xlsx
+++ b/modules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\josh\kenyaEMR-modules-updater\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D764FFF-16C5-4BF8-B750-5A4895EACD85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA49C8B0-46D5-4C76-81B0-BCCA73329524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7576F9BB-DBC4-4D03-8B1C-D88545B56239}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="66">
   <si>
     <t>modules</t>
   </si>
@@ -230,6 +230,12 @@
   </si>
   <si>
     <t>https://github.com/Palladium-hub/openmrs-module-vdot.git</t>
+  </si>
+  <si>
+    <t>bedmanagement</t>
+  </si>
+  <si>
+    <t>https://github.com/Palladium-hub/openmrs-module-bedmanagement.git</t>
   </si>
 </sst>
 </file>
@@ -274,9 +280,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -592,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
@@ -637,11 +644,11 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
+      <c r="A4" s="2" t="s">
+        <v>64</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
@@ -649,32 +656,32 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
@@ -682,32 +689,32 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
@@ -715,10 +722,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
         <v>27</v>
@@ -726,10 +733,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
         <v>27</v>
@@ -737,10 +744,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
         <v>27</v>
@@ -748,10 +755,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
         <v>27</v>
@@ -759,10 +766,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C15" t="s">
         <v>27</v>
@@ -770,10 +777,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C16" t="s">
         <v>27</v>
@@ -781,10 +788,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
         <v>27</v>
@@ -792,10 +799,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
         <v>27</v>
@@ -803,10 +810,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
         <v>27</v>
@@ -814,10 +821,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
         <v>27</v>
@@ -825,10 +832,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
         <v>27</v>
@@ -836,78 +843,89 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C29" t="s">
         <v>27</v>
       </c>
     </row>
@@ -915,32 +933,33 @@
   <autoFilter ref="A1:D28" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{FB795B93-36B6-46BF-94E9-0038AB747753}"/>
-    <hyperlink ref="B4" r:id="rId2" xr:uid="{57F27C2F-EF1E-45D3-B84E-27C348EA6A19}"/>
-    <hyperlink ref="B5" r:id="rId3" xr:uid="{394E958F-8195-420D-9743-5785635638A1}"/>
-    <hyperlink ref="B6" r:id="rId4" xr:uid="{FBE482EB-5021-4FB1-82FA-D062764CA1EB}"/>
-    <hyperlink ref="B7" r:id="rId5" xr:uid="{DBC906DF-0512-4F96-9980-1283786FC3BB}"/>
-    <hyperlink ref="B8" r:id="rId6" xr:uid="{30D882E1-E2EA-46AC-AADB-9448D1E01D5C}"/>
-    <hyperlink ref="B9" r:id="rId7" xr:uid="{6536EB8A-DA8E-4D0F-8593-FB4B5284D1A1}"/>
-    <hyperlink ref="B10" r:id="rId8" xr:uid="{6E470327-BDE8-411E-99F2-E8E5EC5BC4B5}"/>
-    <hyperlink ref="B11" r:id="rId9" xr:uid="{5CDDECC4-987C-4EF8-AAEE-D542DDB2E01A}"/>
-    <hyperlink ref="B12" r:id="rId10" xr:uid="{CB1A6B4D-F0B6-4F48-903E-DD67447B0D1E}"/>
-    <hyperlink ref="B13" r:id="rId11" xr:uid="{0A21E91B-C5AF-4E93-B298-37D3D20820BA}"/>
-    <hyperlink ref="B14" r:id="rId12" xr:uid="{82F1BD6D-109B-4F57-B429-F2C0A2DF5539}"/>
-    <hyperlink ref="B15" r:id="rId13" xr:uid="{CEFE724D-0289-4516-B679-5972075F9D45}"/>
-    <hyperlink ref="B16" r:id="rId14" xr:uid="{9E0376B5-01C2-4493-9DBE-E1898317C082}"/>
-    <hyperlink ref="B17" r:id="rId15" xr:uid="{5114C9EC-EEB3-4299-A9FD-2983F25CB21B}"/>
-    <hyperlink ref="B19" r:id="rId16" xr:uid="{A430A9C6-FD58-4DE8-82B1-C2BDC43CD75D}"/>
-    <hyperlink ref="B20" r:id="rId17" xr:uid="{4BA87FC2-2482-47F3-AF0B-26573751D1D0}"/>
-    <hyperlink ref="B21" r:id="rId18" xr:uid="{CF736F36-5C13-46BF-8EFE-00A8F71CDBFA}"/>
-    <hyperlink ref="B22" r:id="rId19" xr:uid="{F3EE1F0F-3E4B-4FFA-A948-D718624032D3}"/>
-    <hyperlink ref="B23" r:id="rId20" xr:uid="{24CA94E5-1C41-4A90-8A88-F60639278F60}"/>
-    <hyperlink ref="B28" r:id="rId21" xr:uid="{A55B142A-1F76-4FA4-8825-61B2F7CC0A1C}"/>
-    <hyperlink ref="B27" r:id="rId22" xr:uid="{3B59B242-3FBC-42FA-A878-6E97732489BB}"/>
-    <hyperlink ref="B26" r:id="rId23" xr:uid="{7F43F908-E262-4C52-A283-BC53176A8C46}"/>
-    <hyperlink ref="B24" r:id="rId24" xr:uid="{9911E7B8-06C5-456A-9C67-209E377DE4D4}"/>
+    <hyperlink ref="B5" r:id="rId2" xr:uid="{57F27C2F-EF1E-45D3-B84E-27C348EA6A19}"/>
+    <hyperlink ref="B6" r:id="rId3" xr:uid="{394E958F-8195-420D-9743-5785635638A1}"/>
+    <hyperlink ref="B7" r:id="rId4" xr:uid="{FBE482EB-5021-4FB1-82FA-D062764CA1EB}"/>
+    <hyperlink ref="B8" r:id="rId5" xr:uid="{DBC906DF-0512-4F96-9980-1283786FC3BB}"/>
+    <hyperlink ref="B9" r:id="rId6" xr:uid="{30D882E1-E2EA-46AC-AADB-9448D1E01D5C}"/>
+    <hyperlink ref="B10" r:id="rId7" xr:uid="{6536EB8A-DA8E-4D0F-8593-FB4B5284D1A1}"/>
+    <hyperlink ref="B11" r:id="rId8" xr:uid="{6E470327-BDE8-411E-99F2-E8E5EC5BC4B5}"/>
+    <hyperlink ref="B12" r:id="rId9" xr:uid="{5CDDECC4-987C-4EF8-AAEE-D542DDB2E01A}"/>
+    <hyperlink ref="B13" r:id="rId10" xr:uid="{CB1A6B4D-F0B6-4F48-903E-DD67447B0D1E}"/>
+    <hyperlink ref="B14" r:id="rId11" xr:uid="{0A21E91B-C5AF-4E93-B298-37D3D20820BA}"/>
+    <hyperlink ref="B15" r:id="rId12" xr:uid="{82F1BD6D-109B-4F57-B429-F2C0A2DF5539}"/>
+    <hyperlink ref="B16" r:id="rId13" xr:uid="{CEFE724D-0289-4516-B679-5972075F9D45}"/>
+    <hyperlink ref="B17" r:id="rId14" xr:uid="{9E0376B5-01C2-4493-9DBE-E1898317C082}"/>
+    <hyperlink ref="B18" r:id="rId15" xr:uid="{5114C9EC-EEB3-4299-A9FD-2983F25CB21B}"/>
+    <hyperlink ref="B20" r:id="rId16" xr:uid="{A430A9C6-FD58-4DE8-82B1-C2BDC43CD75D}"/>
+    <hyperlink ref="B21" r:id="rId17" xr:uid="{4BA87FC2-2482-47F3-AF0B-26573751D1D0}"/>
+    <hyperlink ref="B22" r:id="rId18" xr:uid="{CF736F36-5C13-46BF-8EFE-00A8F71CDBFA}"/>
+    <hyperlink ref="B23" r:id="rId19" xr:uid="{F3EE1F0F-3E4B-4FFA-A948-D718624032D3}"/>
+    <hyperlink ref="B24" r:id="rId20" xr:uid="{24CA94E5-1C41-4A90-8A88-F60639278F60}"/>
+    <hyperlink ref="B29" r:id="rId21" xr:uid="{A55B142A-1F76-4FA4-8825-61B2F7CC0A1C}"/>
+    <hyperlink ref="B28" r:id="rId22" xr:uid="{3B59B242-3FBC-42FA-A878-6E97732489BB}"/>
+    <hyperlink ref="B27" r:id="rId23" xr:uid="{7F43F908-E262-4C52-A283-BC53176A8C46}"/>
+    <hyperlink ref="B25" r:id="rId24" xr:uid="{9911E7B8-06C5-456A-9C67-209E377DE4D4}"/>
     <hyperlink ref="B3" r:id="rId25" xr:uid="{9B7024D0-965C-4E36-8BBD-D2B5693F8066}"/>
-    <hyperlink ref="B18" r:id="rId26" xr:uid="{5790DF07-3821-4131-B34A-23B6360A489F}"/>
-    <hyperlink ref="B25" r:id="rId27" xr:uid="{4AEA6BB0-8BA5-4D64-85BA-BBC654A24D26}"/>
+    <hyperlink ref="B19" r:id="rId26" xr:uid="{5790DF07-3821-4131-B34A-23B6360A489F}"/>
+    <hyperlink ref="B26" r:id="rId27" xr:uid="{4AEA6BB0-8BA5-4D64-85BA-BBC654A24D26}"/>
+    <hyperlink ref="B4" r:id="rId28" xr:uid="{EE2253DE-D85F-4DEC-8777-34D0879708B6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/modules.xlsx
+++ b/modules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\josh\kenyaEMR-modules-updater\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA49C8B0-46D5-4C76-81B0-BCCA73329524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA0CC989-6884-4B80-B084-9D1381A1F89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7576F9BB-DBC4-4D03-8B1C-D88545B56239}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="62">
   <si>
     <t>modules</t>
   </si>
@@ -109,9 +109,6 @@
     <t>stockmanagement</t>
   </si>
   <si>
-    <t>teleconsultation</t>
-  </si>
-  <si>
     <t>vdot</t>
   </si>
   <si>
@@ -136,9 +133,6 @@
     <t>tag</t>
   </si>
   <si>
-    <t>https://github.com/makombe/openmrs-module-teleconsultation.git</t>
-  </si>
-  <si>
     <t>queue</t>
   </si>
   <si>
@@ -230,12 +224,6 @@
   </si>
   <si>
     <t>https://github.com/Palladium-hub/openmrs-module-vdot.git</t>
-  </si>
-  <si>
-    <t>bedmanagement</t>
-  </si>
-  <si>
-    <t>https://github.com/Palladium-hub/openmrs-module-bedmanagement.git</t>
   </si>
 </sst>
 </file>
@@ -280,10 +268,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -599,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
@@ -612,13 +599,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" t="s">
-        <v>26</v>
-      </c>
       <c r="D1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -626,10 +613,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -637,329 +624,305 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>64</v>
+      <c r="A4" t="s">
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D28" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{FB795B93-36B6-46BF-94E9-0038AB747753}"/>
-    <hyperlink ref="B5" r:id="rId2" xr:uid="{57F27C2F-EF1E-45D3-B84E-27C348EA6A19}"/>
-    <hyperlink ref="B6" r:id="rId3" xr:uid="{394E958F-8195-420D-9743-5785635638A1}"/>
-    <hyperlink ref="B7" r:id="rId4" xr:uid="{FBE482EB-5021-4FB1-82FA-D062764CA1EB}"/>
-    <hyperlink ref="B8" r:id="rId5" xr:uid="{DBC906DF-0512-4F96-9980-1283786FC3BB}"/>
-    <hyperlink ref="B9" r:id="rId6" xr:uid="{30D882E1-E2EA-46AC-AADB-9448D1E01D5C}"/>
-    <hyperlink ref="B10" r:id="rId7" xr:uid="{6536EB8A-DA8E-4D0F-8593-FB4B5284D1A1}"/>
-    <hyperlink ref="B11" r:id="rId8" xr:uid="{6E470327-BDE8-411E-99F2-E8E5EC5BC4B5}"/>
-    <hyperlink ref="B12" r:id="rId9" xr:uid="{5CDDECC4-987C-4EF8-AAEE-D542DDB2E01A}"/>
-    <hyperlink ref="B13" r:id="rId10" xr:uid="{CB1A6B4D-F0B6-4F48-903E-DD67447B0D1E}"/>
-    <hyperlink ref="B14" r:id="rId11" xr:uid="{0A21E91B-C5AF-4E93-B298-37D3D20820BA}"/>
-    <hyperlink ref="B15" r:id="rId12" xr:uid="{82F1BD6D-109B-4F57-B429-F2C0A2DF5539}"/>
-    <hyperlink ref="B16" r:id="rId13" xr:uid="{CEFE724D-0289-4516-B679-5972075F9D45}"/>
-    <hyperlink ref="B17" r:id="rId14" xr:uid="{9E0376B5-01C2-4493-9DBE-E1898317C082}"/>
-    <hyperlink ref="B18" r:id="rId15" xr:uid="{5114C9EC-EEB3-4299-A9FD-2983F25CB21B}"/>
-    <hyperlink ref="B20" r:id="rId16" xr:uid="{A430A9C6-FD58-4DE8-82B1-C2BDC43CD75D}"/>
-    <hyperlink ref="B21" r:id="rId17" xr:uid="{4BA87FC2-2482-47F3-AF0B-26573751D1D0}"/>
-    <hyperlink ref="B22" r:id="rId18" xr:uid="{CF736F36-5C13-46BF-8EFE-00A8F71CDBFA}"/>
-    <hyperlink ref="B23" r:id="rId19" xr:uid="{F3EE1F0F-3E4B-4FFA-A948-D718624032D3}"/>
-    <hyperlink ref="B24" r:id="rId20" xr:uid="{24CA94E5-1C41-4A90-8A88-F60639278F60}"/>
-    <hyperlink ref="B29" r:id="rId21" xr:uid="{A55B142A-1F76-4FA4-8825-61B2F7CC0A1C}"/>
-    <hyperlink ref="B28" r:id="rId22" xr:uid="{3B59B242-3FBC-42FA-A878-6E97732489BB}"/>
-    <hyperlink ref="B27" r:id="rId23" xr:uid="{7F43F908-E262-4C52-A283-BC53176A8C46}"/>
-    <hyperlink ref="B25" r:id="rId24" xr:uid="{9911E7B8-06C5-456A-9C67-209E377DE4D4}"/>
-    <hyperlink ref="B3" r:id="rId25" xr:uid="{9B7024D0-965C-4E36-8BBD-D2B5693F8066}"/>
-    <hyperlink ref="B19" r:id="rId26" xr:uid="{5790DF07-3821-4131-B34A-23B6360A489F}"/>
-    <hyperlink ref="B26" r:id="rId27" xr:uid="{4AEA6BB0-8BA5-4D64-85BA-BBC654A24D26}"/>
-    <hyperlink ref="B4" r:id="rId28" xr:uid="{EE2253DE-D85F-4DEC-8777-34D0879708B6}"/>
+    <hyperlink ref="B4" r:id="rId2" xr:uid="{57F27C2F-EF1E-45D3-B84E-27C348EA6A19}"/>
+    <hyperlink ref="B5" r:id="rId3" xr:uid="{394E958F-8195-420D-9743-5785635638A1}"/>
+    <hyperlink ref="B6" r:id="rId4" xr:uid="{FBE482EB-5021-4FB1-82FA-D062764CA1EB}"/>
+    <hyperlink ref="B7" r:id="rId5" xr:uid="{DBC906DF-0512-4F96-9980-1283786FC3BB}"/>
+    <hyperlink ref="B8" r:id="rId6" xr:uid="{30D882E1-E2EA-46AC-AADB-9448D1E01D5C}"/>
+    <hyperlink ref="B9" r:id="rId7" xr:uid="{6536EB8A-DA8E-4D0F-8593-FB4B5284D1A1}"/>
+    <hyperlink ref="B10" r:id="rId8" xr:uid="{6E470327-BDE8-411E-99F2-E8E5EC5BC4B5}"/>
+    <hyperlink ref="B11" r:id="rId9" xr:uid="{5CDDECC4-987C-4EF8-AAEE-D542DDB2E01A}"/>
+    <hyperlink ref="B12" r:id="rId10" xr:uid="{CB1A6B4D-F0B6-4F48-903E-DD67447B0D1E}"/>
+    <hyperlink ref="B13" r:id="rId11" xr:uid="{0A21E91B-C5AF-4E93-B298-37D3D20820BA}"/>
+    <hyperlink ref="B14" r:id="rId12" xr:uid="{82F1BD6D-109B-4F57-B429-F2C0A2DF5539}"/>
+    <hyperlink ref="B15" r:id="rId13" xr:uid="{CEFE724D-0289-4516-B679-5972075F9D45}"/>
+    <hyperlink ref="B16" r:id="rId14" xr:uid="{9E0376B5-01C2-4493-9DBE-E1898317C082}"/>
+    <hyperlink ref="B17" r:id="rId15" xr:uid="{5114C9EC-EEB3-4299-A9FD-2983F25CB21B}"/>
+    <hyperlink ref="B19" r:id="rId16" xr:uid="{A430A9C6-FD58-4DE8-82B1-C2BDC43CD75D}"/>
+    <hyperlink ref="B20" r:id="rId17" xr:uid="{4BA87FC2-2482-47F3-AF0B-26573751D1D0}"/>
+    <hyperlink ref="B21" r:id="rId18" xr:uid="{CF736F36-5C13-46BF-8EFE-00A8F71CDBFA}"/>
+    <hyperlink ref="B22" r:id="rId19" xr:uid="{F3EE1F0F-3E4B-4FFA-A948-D718624032D3}"/>
+    <hyperlink ref="B23" r:id="rId20" xr:uid="{24CA94E5-1C41-4A90-8A88-F60639278F60}"/>
+    <hyperlink ref="B26" r:id="rId21" xr:uid="{7F43F908-E262-4C52-A283-BC53176A8C46}"/>
+    <hyperlink ref="B24" r:id="rId22" xr:uid="{9911E7B8-06C5-456A-9C67-209E377DE4D4}"/>
+    <hyperlink ref="B3" r:id="rId23" xr:uid="{9B7024D0-965C-4E36-8BBD-D2B5693F8066}"/>
+    <hyperlink ref="B18" r:id="rId24" xr:uid="{5790DF07-3821-4131-B34A-23B6360A489F}"/>
+    <hyperlink ref="B25" r:id="rId25" xr:uid="{4AEA6BB0-8BA5-4D64-85BA-BBC654A24D26}"/>
+    <hyperlink ref="B27" r:id="rId26" xr:uid="{A55B142A-1F76-4FA4-8825-61B2F7CC0A1C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/modules.xlsx
+++ b/modules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\josh\kenyaEMR-modules-updater\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA0CC989-6884-4B80-B084-9D1381A1F89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73D4AFA-C0D2-4E90-816B-C347854C8B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7576F9BB-DBC4-4D03-8B1C-D88545B56239}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="60">
   <si>
     <t>modules</t>
   </si>
@@ -145,13 +145,7 @@
     <t>kenyaemrpsmart</t>
   </si>
   <si>
-    <t>spreadsheetimport</t>
-  </si>
-  <si>
     <t>https://github.com/Palladium-hub/openmrs-module-kenyaemrpsmart.git</t>
-  </si>
-  <si>
-    <t>https://github.com/Palladium-hub/openmrs-module-spreadsheetimport.git</t>
   </si>
   <si>
     <t>https://github.com/Palladium-hub/openmrs-module-afyastat.git</t>
@@ -586,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
@@ -613,7 +607,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
@@ -624,7 +618,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
@@ -635,7 +629,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
         <v>26</v>
@@ -646,7 +640,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
         <v>28</v>
@@ -657,7 +651,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
         <v>26</v>
@@ -668,7 +662,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
@@ -679,7 +673,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
         <v>29</v>
@@ -690,7 +684,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
         <v>26</v>
@@ -701,7 +695,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
@@ -712,7 +706,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>26</v>
@@ -723,7 +717,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
         <v>26</v>
@@ -734,7 +728,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
         <v>26</v>
@@ -745,7 +739,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C14" t="s">
         <v>26</v>
@@ -756,7 +750,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
         <v>26</v>
@@ -767,7 +761,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
         <v>26</v>
@@ -778,7 +772,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
         <v>26</v>
@@ -789,7 +783,7 @@
         <v>34</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
         <v>26</v>
@@ -800,7 +794,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
         <v>26</v>
@@ -811,7 +805,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C20" t="s">
         <v>26</v>
@@ -822,7 +816,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
         <v>26</v>
@@ -833,7 +827,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C22" t="s">
         <v>28</v>
@@ -844,7 +838,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C23" t="s">
         <v>26</v>
@@ -855,7 +849,7 @@
         <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C24" t="s">
         <v>32</v>
@@ -863,39 +857,28 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C27" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D28" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}"/>
+  <autoFilter ref="A1:D27" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{FB795B93-36B6-46BF-94E9-0038AB747753}"/>
     <hyperlink ref="B4" r:id="rId2" xr:uid="{57F27C2F-EF1E-45D3-B84E-27C348EA6A19}"/>
@@ -917,12 +900,11 @@
     <hyperlink ref="B21" r:id="rId18" xr:uid="{CF736F36-5C13-46BF-8EFE-00A8F71CDBFA}"/>
     <hyperlink ref="B22" r:id="rId19" xr:uid="{F3EE1F0F-3E4B-4FFA-A948-D718624032D3}"/>
     <hyperlink ref="B23" r:id="rId20" xr:uid="{24CA94E5-1C41-4A90-8A88-F60639278F60}"/>
-    <hyperlink ref="B26" r:id="rId21" xr:uid="{7F43F908-E262-4C52-A283-BC53176A8C46}"/>
+    <hyperlink ref="B25" r:id="rId21" xr:uid="{7F43F908-E262-4C52-A283-BC53176A8C46}"/>
     <hyperlink ref="B24" r:id="rId22" xr:uid="{9911E7B8-06C5-456A-9C67-209E377DE4D4}"/>
     <hyperlink ref="B3" r:id="rId23" xr:uid="{9B7024D0-965C-4E36-8BBD-D2B5693F8066}"/>
     <hyperlink ref="B18" r:id="rId24" xr:uid="{5790DF07-3821-4131-B34A-23B6360A489F}"/>
-    <hyperlink ref="B25" r:id="rId25" xr:uid="{4AEA6BB0-8BA5-4D64-85BA-BBC654A24D26}"/>
-    <hyperlink ref="B27" r:id="rId26" xr:uid="{A55B142A-1F76-4FA4-8825-61B2F7CC0A1C}"/>
+    <hyperlink ref="B26" r:id="rId25" xr:uid="{A55B142A-1F76-4FA4-8825-61B2F7CC0A1C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/modules.xlsx
+++ b/modules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\josh\kenyaEMR-modules-updater\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73D4AFA-C0D2-4E90-816B-C347854C8B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2700F383-520F-41CA-8812-C91BA3584E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7576F9BB-DBC4-4D03-8B1C-D88545B56239}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="58">
   <si>
     <t>modules</t>
   </si>
@@ -140,12 +140,6 @@
   </si>
   <si>
     <t>stock-2.8.4-platform</t>
-  </si>
-  <si>
-    <t>kenyaemrpsmart</t>
-  </si>
-  <si>
-    <t>https://github.com/Palladium-hub/openmrs-module-kenyaemrpsmart.git</t>
   </si>
   <si>
     <t>https://github.com/Palladium-hub/openmrs-module-afyastat.git</t>
@@ -580,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
@@ -607,7 +601,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
@@ -618,7 +612,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
@@ -629,7 +623,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
         <v>26</v>
@@ -640,7 +634,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
         <v>28</v>
@@ -651,7 +645,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
         <v>26</v>
@@ -662,7 +656,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
@@ -673,7 +667,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
         <v>29</v>
@@ -684,7 +678,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
         <v>26</v>
@@ -695,7 +689,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
@@ -706,7 +700,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
         <v>26</v>
@@ -717,7 +711,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>26</v>
@@ -728,7 +722,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
         <v>26</v>
@@ -739,7 +733,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
         <v>26</v>
@@ -750,7 +744,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
         <v>26</v>
@@ -761,7 +755,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
         <v>26</v>
@@ -772,7 +766,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
         <v>26</v>
@@ -780,10 +774,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
         <v>26</v>
@@ -791,10 +785,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C19" t="s">
         <v>26</v>
@@ -802,10 +796,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
         <v>26</v>
@@ -813,72 +807,61 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D27" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}"/>
+  <autoFilter ref="A1:D26" xr:uid="{9D447332-634A-4264-831A-AFF551D7ED1B}"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{FB795B93-36B6-46BF-94E9-0038AB747753}"/>
     <hyperlink ref="B4" r:id="rId2" xr:uid="{57F27C2F-EF1E-45D3-B84E-27C348EA6A19}"/>
@@ -895,16 +878,15 @@
     <hyperlink ref="B15" r:id="rId13" xr:uid="{CEFE724D-0289-4516-B679-5972075F9D45}"/>
     <hyperlink ref="B16" r:id="rId14" xr:uid="{9E0376B5-01C2-4493-9DBE-E1898317C082}"/>
     <hyperlink ref="B17" r:id="rId15" xr:uid="{5114C9EC-EEB3-4299-A9FD-2983F25CB21B}"/>
-    <hyperlink ref="B19" r:id="rId16" xr:uid="{A430A9C6-FD58-4DE8-82B1-C2BDC43CD75D}"/>
-    <hyperlink ref="B20" r:id="rId17" xr:uid="{4BA87FC2-2482-47F3-AF0B-26573751D1D0}"/>
-    <hyperlink ref="B21" r:id="rId18" xr:uid="{CF736F36-5C13-46BF-8EFE-00A8F71CDBFA}"/>
-    <hyperlink ref="B22" r:id="rId19" xr:uid="{F3EE1F0F-3E4B-4FFA-A948-D718624032D3}"/>
-    <hyperlink ref="B23" r:id="rId20" xr:uid="{24CA94E5-1C41-4A90-8A88-F60639278F60}"/>
-    <hyperlink ref="B25" r:id="rId21" xr:uid="{7F43F908-E262-4C52-A283-BC53176A8C46}"/>
-    <hyperlink ref="B24" r:id="rId22" xr:uid="{9911E7B8-06C5-456A-9C67-209E377DE4D4}"/>
+    <hyperlink ref="B18" r:id="rId16" xr:uid="{A430A9C6-FD58-4DE8-82B1-C2BDC43CD75D}"/>
+    <hyperlink ref="B19" r:id="rId17" xr:uid="{4BA87FC2-2482-47F3-AF0B-26573751D1D0}"/>
+    <hyperlink ref="B20" r:id="rId18" xr:uid="{CF736F36-5C13-46BF-8EFE-00A8F71CDBFA}"/>
+    <hyperlink ref="B21" r:id="rId19" xr:uid="{F3EE1F0F-3E4B-4FFA-A948-D718624032D3}"/>
+    <hyperlink ref="B22" r:id="rId20" xr:uid="{24CA94E5-1C41-4A90-8A88-F60639278F60}"/>
+    <hyperlink ref="B24" r:id="rId21" xr:uid="{7F43F908-E262-4C52-A283-BC53176A8C46}"/>
+    <hyperlink ref="B23" r:id="rId22" xr:uid="{9911E7B8-06C5-456A-9C67-209E377DE4D4}"/>
     <hyperlink ref="B3" r:id="rId23" xr:uid="{9B7024D0-965C-4E36-8BBD-D2B5693F8066}"/>
-    <hyperlink ref="B18" r:id="rId24" xr:uid="{5790DF07-3821-4131-B34A-23B6360A489F}"/>
-    <hyperlink ref="B26" r:id="rId25" xr:uid="{A55B142A-1F76-4FA4-8825-61B2F7CC0A1C}"/>
+    <hyperlink ref="B25" r:id="rId24" xr:uid="{A55B142A-1F76-4FA4-8825-61B2F7CC0A1C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
